--- a/PSR-FREEZER-2026-01-23-to-2026-01-23 (1).xlsx
+++ b/PSR-FREEZER-2026-01-23-to-2026-01-23 (1).xlsx
@@ -1210,8 +1210,7 @@
     <t>1967207</t>
   </si>
   <si>
-    <t>Mat og helse, b-bygg
-Leveres før lunsj</t>
+    <t xml:space="preserve">Note 10</t>
   </si>
   <si>
     <t>Pølsebrød Hatting Pose 12x45g</t>
